--- a/需求文档/我们的餐桌-模块功能开发计划.xlsx
+++ b/需求文档/我们的餐桌-模块功能开发计划.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进度总览" sheetId="1" r:id="R7874178f6f07453c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发清单" sheetId="2" r:id="R29066b1f6bc4425a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收清单" sheetId="3" r:id="R487132c471e54a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进度总览" sheetId="1" r:id="Rb92a732a9b9a4768"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发清单" sheetId="2" r:id="Ra0fb15fcb0e449c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收清单" sheetId="3" r:id="R0e89a6c785e247e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -440,7 +440,7 @@
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>基线：需求 v1.5 · 三服务技术设计 v1.2 · UI v5 · Flyway V1/V2    |    更新日期：2026-09-21</x:v>
+        <x:v>基线：需求 v1.5 · 三服务技术设计 v1.13 · UI v5 · Flyway V1—V10    |    更新日期：2026-10-08</x:v>
       </x:c>
       <x:c r="B4" s="2"/>
       <x:c r="C4" s="2"/>
@@ -610,7 +610,7 @@
       </x:c>
       <x:c r="D13" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A13,'开发清单'!$A$8:$A$95,"◐ 进行中")</x:f>
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E13" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A13,'开发清单'!$A$8:$A$95,"⚠ 阻塞")</x:f>
@@ -637,11 +637,11 @@
       </x:c>
       <x:c r="D14" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A14,'开发清单'!$A$8:$A$95,"◐ 进行中")</x:f>
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A14,'开发清单'!$A$8:$A$95,"⚠ 阻塞")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="13" t="n">
         <x:f>IF(B14=0,0,C14/B14)</x:f>
@@ -664,11 +664,11 @@
       </x:c>
       <x:c r="D15" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A15,'开发清单'!$A$8:$A$95,"◐ 进行中")</x:f>
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E15" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A15,'开发清单'!$A$8:$A$95,"⚠ 阻塞")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="13" t="n">
         <x:f>IF(B15=0,0,C15/B15)</x:f>
@@ -718,7 +718,7 @@
       </x:c>
       <x:c r="D17" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A17,'开发清单'!$A$8:$A$95,"◐ 进行中")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E17" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A17,'开发清单'!$A$8:$A$95,"⚠ 阻塞")</x:f>
@@ -745,11 +745,11 @@
       </x:c>
       <x:c r="D18" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A18,'开发清单'!$A$8:$A$95,"◐ 进行中")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E18" s="2" t="n">
         <x:f>COUNTIFS('开发清单'!$D$8:$D$95,A18,'开发清单'!$A$8:$A$95,"⚠ 阻塞")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="13" t="n">
         <x:f>IF(B18=0,0,C18/B18)</x:f>
@@ -1406,7 +1406,7 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>⚠ 阻塞</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
         <x:v>DEV-001</x:v>
@@ -1436,16 +1436,18 @@
         <x:v>技术实施（建议必需）
 技术§17</x:v>
       </x:c>
-      <x:c r="K8" s="11"/>
+      <x:c r="K8" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L8" s="12"/>
       <x:c r="M8" s="12"/>
       <x:c r="N8" s="11" t="str">
-        <x:v>等待小程序AppID及域名；本地MySQL/Redis连接已验证。</x:v>
+        <x:v>AppID与本地AppSecret已生效，开发者工具及三服务可用；真实登录通过。HTTPS域名、第二位测试成员及存储选型待准备。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="78" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>⚠ 阻塞</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
         <x:v>DEV-002</x:v>
@@ -1475,16 +1477,18 @@
         <x:v>技术实施（建议必需）
 技术§3.2、3.8、17</x:v>
       </x:c>
-      <x:c r="K9" s="11"/>
+      <x:c r="K9" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L9" s="12"/>
       <x:c r="M9" s="12"/>
       <x:c r="N9" s="11" t="str">
-        <x:v>官方登录适配器已实现；缺少AppID/AppSecret，尚无真实微信与内容安全结果。</x:v>
+        <x:v>模拟器真实微信code换身份、自动注册和重登去重通过；默认昵称已显示。昵称头像填写方式及内容安全能力仍待验证。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="78" customHeight="1">
       <x:c r="A10" s="11" t="str">
-        <x:v>⚠ 阻塞</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
         <x:v>DEV-003</x:v>
@@ -1514,11 +1518,13 @@
         <x:v>技术实施（建议必需）
 技术§9.3、17</x:v>
       </x:c>
-      <x:c r="K10" s="11"/>
+      <x:c r="K10" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L10" s="12"/>
       <x:c r="M10" s="12"/>
       <x:c r="N10" s="11" t="str">
-        <x:v>等待真实小程序类目、订阅模板及授权联调。</x:v>
+        <x:v>3988/6633模板已获批，字段与授权、发送跳转代码已接；新订单预约时间待确认，真实微信回执与跳转待验收。 详见开发记录/2026-10-05-微信订阅通知.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="78" customHeight="1">
@@ -1760,7 +1766,7 @@
       <x:c r="L16" s="12"/>
       <x:c r="M16" s="12"/>
       <x:c r="N16" s="11" t="str">
-        <x:v>三服务共享令牌摘要解析及数据库资格读取；日常/主厨已验证，聚会与评价资源范围待实现。</x:v>
+        <x:v>三服务共享会话与权限上下文；日常/主厨、评价受限、聚会成员和密令过期保留原聚会资格通过，真实设备路由待验收。 详见开发记录/2026-10-05-聚会基础.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="78" customHeight="1">
@@ -1844,7 +1850,7 @@
       <x:c r="L18" s="12"/>
       <x:c r="M18" s="12"/>
       <x:c r="N18" s="11" t="str">
-        <x:v>UTC/北京时间、凌晨宵夜及截止边界测试通过；各领域容量限制待接入。</x:v>
+        <x:v>采购500项、100人及Unicode输入上限已验证；全局规则与双真机仍待收口。 详见开发记录/2026-10-05-聚会采购.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="78" customHeight="1">
@@ -1969,7 +1975,7 @@
       <x:c r="L21" s="12"/>
       <x:c r="M21" s="12"/>
       <x:c r="N21" s="11" t="str">
-        <x:v>原生TS、五Tab、主厨分包与请求层通过类型检查；真实会话刷新、邀请和业务幂等联调待完成。</x:v>
+        <x:v>前端75项测试、21页WXML/18份WXSS编译通过；封面选择及回退已接通，发布域名与真机待验收。 详见开发记录/2026-10-08-聚会预设封面.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="78" customHeight="1">
@@ -2010,7 +2016,7 @@
       <x:c r="L22" s="12"/>
       <x:c r="M22" s="12"/>
       <x:c r="N22" s="11" t="str">
-        <x:v>受控绑定命令、事务审计和数据库唯一约束已实现；等待两位主厨真实登录后的内部ID。</x:v>
+        <x:v>本人确认后受控绑定用户1至餐厅1成功；重登保留主厨身份及本店入口。隔离测试通过，第二位真实主厨待登录绑定。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="78" customHeight="1">
@@ -2051,7 +2057,7 @@
       <x:c r="L23" s="12"/>
       <x:c r="M23" s="12"/>
       <x:c r="N23" s="11" t="str">
-        <x:v>注册去重、昵称修改及真实MySQL测试通过；微信身份交换使用测试替身，尚未真实平台验收。</x:v>
+        <x:v>模拟器真实登录注册、退出重登通过，仍为用户1且总用户数为1；默认昵称可见。昵称编辑与历史业务身份归属待完整验收。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="78" customHeight="1">
@@ -2215,12 +2221,12 @@
       <x:c r="L27" s="12"/>
       <x:c r="M27" s="12"/>
       <x:c r="N27" s="11" t="str">
-        <x:v>五Tab及日常准入守卫、我的主厨入口已接入；聚会/评价受限落地页后续实现。</x:v>
+        <x:v>日常五Tab及受限聚会/评价分包已接入；仅聚会资格可从个人中心查记录，不展示日常导航，双真机待验收。 详见开发记录/2026-10-05-聚会基础.md。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="78" customHeight="1">
       <x:c r="A28" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
         <x:v>DEV-021</x:v>
@@ -2250,14 +2256,18 @@
         <x:v>技术实施（建议必需）
 技术§7、8</x:v>
       </x:c>
-      <x:c r="K28" s="11"/>
+      <x:c r="K28" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L28" s="12"/>
       <x:c r="M28" s="12"/>
-      <x:c r="N28" s="11"/>
+      <x:c r="N28" s="11" t="str">
+        <x:v>首页统计60秒缓存、事务提交换代、迟到旧写入隔离、Redis故障回源及推荐MySQL持久化通过；其他模块缓存与短锁后续。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="78" customHeight="1">
       <x:c r="A29" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B29" s="6" t="str">
         <x:v>DEV-022</x:v>
@@ -2287,14 +2297,18 @@
         <x:v>FR-ADM-07、FR-ADM-08
 技术§3.3、3.8、5.3</x:v>
       </x:c>
-      <x:c r="K29" s="11"/>
+      <x:c r="K29" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L29" s="12"/>
       <x:c r="M29" s="12"/>
-      <x:c r="N29" s="11"/>
+      <x:c r="N29" s="11" t="str">
+        <x:v>餐厅名称维护、本店权限与版本控制已实现并通过数据库接口测试；封面上传及真机验收待完成。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="78" customHeight="1">
       <x:c r="A30" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B30" s="6" t="str">
         <x:v>DEV-023</x:v>
@@ -2324,14 +2338,18 @@
         <x:v>FR-ADM-09、FR-ADM-10、FR-ADM-12
 技术§3.3、5.3</x:v>
       </x:c>
-      <x:c r="K30" s="11"/>
+      <x:c r="K30" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L30" s="12"/>
       <x:c r="M30" s="12"/>
-      <x:c r="N30" s="11"/>
+      <x:c r="N30" s="11" t="str">
+        <x:v>品类增改删、同店重名、固定季节品类保护、含下架菜不可删除、同店移动菜品已实现并验证；页面已接入，待微信交互验收。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="78" customHeight="1">
       <x:c r="A31" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B31" s="6" t="str">
         <x:v>DEV-024</x:v>
@@ -2361,14 +2379,18 @@
         <x:v>FR-ADM-13、FR-ADM-14
 技术§3.3、10.2</x:v>
       </x:c>
-      <x:c r="K31" s="11"/>
+      <x:c r="K31" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L31" s="12"/>
       <x:c r="M31" s="12"/>
-      <x:c r="N31" s="11"/>
+      <x:c r="N31" s="11" t="str">
+        <x:v>菜品文字/做法维护、20/50/500字校验及顾客字段隔离已实现并验证；图片与真机验收待完成。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="78" customHeight="1">
       <x:c r="A32" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
         <x:v>DEV-025</x:v>
@@ -2398,14 +2420,18 @@
         <x:v>FR-ADM-15、FR-ADM-16
 技术§3.3</x:v>
       </x:c>
-      <x:c r="K32" s="11"/>
+      <x:c r="K32" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L32" s="12"/>
       <x:c r="M32" s="12"/>
-      <x:c r="N32" s="11"/>
+      <x:c r="N32" s="11" t="str">
+        <x:v>季节月份、空季节品类隐藏、按所选日期筛选、上下架及版本控制通过；页面已接入，正式餐单历史行为与微信交互待验收。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="78" customHeight="1">
       <x:c r="A33" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
         <x:v>DEV-026</x:v>
@@ -2435,14 +2461,18 @@
         <x:v>FR-ADM-17、FR-DATA-02
 技术§3.3、6.6</x:v>
       </x:c>
-      <x:c r="K33" s="11"/>
+      <x:c r="K33" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L33" s="12"/>
       <x:c r="M33" s="12"/>
-      <x:c r="N33" s="11"/>
+      <x:c r="N33" s="11" t="str">
+        <x:v>评价昵称与头像首次快照、200字emoji文本存储通过；历史图片资源保留待接入。 详见开发记录/2026-10-04-评价分享.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="78" customHeight="1">
       <x:c r="A34" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B34" s="6" t="str">
         <x:v>DEV-027</x:v>
@@ -2472,14 +2502,18 @@
         <x:v>FR-ADM-18、FR-ADM-19、FR-ADM-20、FR-ADM-21
 技术§3.3、5.3</x:v>
       </x:c>
-      <x:c r="K34" s="11"/>
+      <x:c r="K34" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L34" s="12"/>
       <x:c r="M34" s="12"/>
-      <x:c r="N34" s="11"/>
+      <x:c r="N34" s="11" t="str">
+        <x:v>规格限额/默认项/整体验证回滚及稳定ID已验证，原生编辑页已接入；待微信交互和历史快照验收。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="78" customHeight="1">
       <x:c r="A35" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
         <x:v>DEV-028</x:v>
@@ -2509,14 +2543,18 @@
         <x:v>FR-ORD-08、FR-ORD-09、FR-ORD-10、FR-ORD-12、FR-ORD-28
 技术§3.3、5.3、10.2</x:v>
       </x:c>
-      <x:c r="K35" s="11"/>
+      <x:c r="K35" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L35" s="12"/>
       <x:c r="M35" s="12"/>
-      <x:c r="N35" s="11"/>
+      <x:c r="N35" s="11" t="str">
+        <x:v>顾客菜单与做法隔离、均分/条数及有效HOT前5已接入；跨店时令与下单复核通过，简介截断和真机后续。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="78" customHeight="1">
       <x:c r="A36" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
         <x:v>DEV-029</x:v>
@@ -2546,10 +2584,14 @@
         <x:v>FR-ORD-01、FR-ORD-02、FR-ORD-03、FR-ORD-05
 技术§3.3、11</x:v>
       </x:c>
-      <x:c r="K36" s="11"/>
+      <x:c r="K36" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L36" s="12"/>
       <x:c r="M36" s="12"/>
-      <x:c r="N36" s="11"/>
+      <x:c r="N36" s="11" t="str">
+        <x:v>双餐厅名称和菜单切换已接入；封面、主厨信息及共享清单保留待后续。 详见开发记录/2026-10-03-菜单基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="78" customHeight="1">
       <x:c r="A37" s="11" t="str">
@@ -2664,7 +2706,7 @@
     </x:row>
     <x:row r="40" ht="78" customHeight="1">
       <x:c r="A40" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B40" s="6" t="str">
         <x:v>DEV-033</x:v>
@@ -2694,14 +2736,18 @@
         <x:v>FR-ME-07、FR-ME-08、FR-ADM-01、FR-ADM-02、FR-ADM-03、FR-ADM-06
 技术§3.1、11</x:v>
       </x:c>
-      <x:c r="K40" s="11"/>
+      <x:c r="K40" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L40" s="12"/>
       <x:c r="M40" s="12"/>
-      <x:c r="N40" s="11"/>
+      <x:c r="N40" s="11" t="str">
+        <x:v>本店餐单入口和详情实际确认已接入；主厨权限隔离通过，今日工作台统计与双真机待验收。 详见开发记录/2026-10-04-实际餐单确认.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="78" customHeight="1">
       <x:c r="A41" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B41" s="6" t="str">
         <x:v>DEV-034</x:v>
@@ -2731,14 +2777,18 @@
         <x:v>FR-ADM-04
 技术§5.4、10.2</x:v>
       </x:c>
-      <x:c r="K41" s="11"/>
+      <x:c r="K41" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L41" s="12"/>
       <x:c r="M41" s="12"/>
-      <x:c r="N41" s="11"/>
+      <x:c r="N41" s="11" t="str">
+        <x:v>V5保存提交时做法，本店主厨专用接口和详情入口已接入，其他人拒绝；空做法编辑入口及真机待验收。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="78" customHeight="1">
       <x:c r="A42" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B42" s="6" t="str">
         <x:v>DEV-035</x:v>
@@ -2768,14 +2818,18 @@
         <x:v>FR-ORD-06、FR-ORD-07
 技术§3.4</x:v>
       </x:c>
-      <x:c r="K42" s="11"/>
+      <x:c r="K42" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L42" s="12"/>
       <x:c r="M42" s="12"/>
-      <x:c r="N42" s="11"/>
+      <x:c r="N42" s="11" t="str">
+        <x:v>服务端可选餐次、默认与凌晨归属、四截止及跨月校验通过；模拟器日期餐次已加载。完成确认页面及双真机边界待验收。 详见开发记录/2026-10-03-共享清单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="78" customHeight="1">
       <x:c r="A43" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B43" s="6" t="str">
         <x:v>DEV-036</x:v>
@@ -2805,14 +2859,18 @@
         <x:v>FR-ORD-04、FR-ORD-18
 技术§3.4、6、8</x:v>
       </x:c>
-      <x:c r="K43" s="11"/>
+      <x:c r="K43" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L43" s="12"/>
       <x:c r="M43" s="12"/>
-      <x:c r="N43" s="11"/>
+      <x:c r="N43" s="11" t="str">
+        <x:v>占用唯一、取消保留历史、明确重建空清单、同键重建与旧单不可复活验证通过，完整双真机待验收。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="78" customHeight="1">
       <x:c r="A44" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B44" s="6" t="str">
         <x:v>DEV-037</x:v>
@@ -2842,14 +2900,18 @@
         <x:v>FR-ORD-13、FR-ORD-15、FR-ORD-16
 技术§3.4、8.2</x:v>
       </x:c>
-      <x:c r="K44" s="11"/>
+      <x:c r="K44" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L44" s="12"/>
       <x:c r="M44" s="12"/>
-      <x:c r="N44" s="11"/>
+      <x:c r="N44" s="11" t="str">
+        <x:v>规格抽屉预选默认项、服务端完整校验、同人归并与跨人分行、代改保留原添加人已实现并测试；双真机交互待验收。 详见开发记录/2026-10-03-共享清单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="78" customHeight="1">
       <x:c r="A45" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B45" s="6" t="str">
         <x:v>DEV-038</x:v>
@@ -2879,14 +2941,18 @@
         <x:v>FR-ORD-14、FR-ORD-17
 技术§5.3—5.5</x:v>
       </x:c>
-      <x:c r="K45" s="11"/>
+      <x:c r="K45" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L45" s="12"/>
       <x:c r="M45" s="12"/>
-      <x:c r="N45" s="11"/>
+      <x:c r="N45" s="11" t="str">
+        <x:v>菜品详情、规格、实时一位小数均分/条数、昵称头像评价分页已接入；真实图片上传和非空双真机待验收。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="78" customHeight="1">
       <x:c r="A46" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B46" s="6" t="str">
         <x:v>DEV-039</x:v>
@@ -2916,14 +2982,18 @@
         <x:v>FR-ORD-19、FR-ORD-20
 技术§3.4、11</x:v>
       </x:c>
-      <x:c r="K46" s="11"/>
+      <x:c r="K46" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L46" s="12"/>
       <x:c r="M46" s="12"/>
-      <x:c r="N46" s="11"/>
+      <x:c r="N46" s="11" t="str">
+        <x:v>正式/待提交分开；道数份数人数、代改、清空只影响待提交及末行明确取消通过测试，非空真机待验收。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="78" customHeight="1">
       <x:c r="A47" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B47" s="6" t="str">
         <x:v>DEV-040</x:v>
@@ -2953,14 +3023,18 @@
         <x:v>FR-ORD-21、FR-ORD-22
 技术§3.4、7、8</x:v>
       </x:c>
-      <x:c r="K47" s="11"/>
+      <x:c r="K47" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L47" s="12"/>
       <x:c r="M47" s="12"/>
-      <x:c r="N47" s="11"/>
+      <x:c r="N47" s="11" t="str">
+        <x:v>2秒轮询、隐藏停止、增量/规格/人数备注冲突与强制复核测试通过，实际双真机3秒可见尚待测量。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="78" customHeight="1">
       <x:c r="A48" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B48" s="6" t="str">
         <x:v>DEV-041</x:v>
@@ -2990,14 +3064,18 @@
         <x:v>FR-ORD-23、FR-ORD-24、FR-ORD-25
 技术§5.4、8</x:v>
       </x:c>
-      <x:c r="K48" s="11"/>
+      <x:c r="K48" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L48" s="12"/>
       <x:c r="M48" s="12"/>
-      <x:c r="N48" s="11"/>
+      <x:c r="N48" s="11" t="str">
+        <x:v>提交页展示最新餐厅日期餐次及参与者，人数备注与快捷标签、变更差异和再次核对已实现测试。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="78" customHeight="1">
       <x:c r="A49" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B49" s="6" t="str">
         <x:v>DEV-042</x:v>
@@ -3027,14 +3105,18 @@
         <x:v>FR-ORD-26、FR-ORD-27
 技术§3.4、8.3—8.4</x:v>
       </x:c>
-      <x:c r="K49" s="11"/>
+      <x:c r="K49" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L49" s="12"/>
       <x:c r="M49" s="12"/>
-      <x:c r="N49" s="11"/>
+      <x:c r="N49" s="11" t="str">
+        <x:v>首次提交直接进行中，同版本并发只一次，事务参与者/Outbox及重复键通过，非空设备流程待验收。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="78" customHeight="1">
       <x:c r="A50" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B50" s="6" t="str">
         <x:v>DEV-043</x:v>
@@ -3064,14 +3146,18 @@
         <x:v>FR-BILL-01、FR-BILL-02、FR-BILL-04
 技术§5.4、10</x:v>
       </x:c>
-      <x:c r="K50" s="11"/>
+      <x:c r="K50" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L50" s="12"/>
       <x:c r="M50" s="12"/>
-      <x:c r="N50" s="11"/>
+      <x:c r="N50" s="11" t="str">
+        <x:v>完成详情已接入实际菜品评价入口和回看；个人评价邀请进度已接入，餐单列表评价进度后续。 详见开发记录/2026-10-04-评价分享.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="78" customHeight="1">
       <x:c r="A51" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B51" s="6" t="str">
         <x:v>DEV-044</x:v>
@@ -3101,14 +3187,18 @@
         <x:v>FR-BILL-09、FR-BILL-10、FR-BILL-11
 技术§3.4、8.4</x:v>
       </x:c>
-      <x:c r="K51" s="11"/>
+      <x:c r="K51" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L51" s="12"/>
       <x:c r="M51" s="12"/>
-      <x:c r="N51" s="11"/>
+      <x:c r="N51" s="11" t="str">
+        <x:v>追加显式归并、正式行代改生效、原添加人保留、99份回滚与截止约束通过，双真机交互待验收。 详见开发记录/2026-10-03-正式下单.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="78" customHeight="1">
       <x:c r="A52" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B52" s="6" t="str">
         <x:v>DEV-045</x:v>
@@ -3138,14 +3228,18 @@
         <x:v>FR-BILL-12、FR-BILL-13、FR-DATA-04
 技术§3.4、8</x:v>
       </x:c>
-      <x:c r="K52" s="11"/>
+      <x:c r="K52" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L52" s="12"/>
       <x:c r="M52" s="12"/>
-      <x:c r="N52" s="11"/>
+      <x:c r="N52" s="11" t="str">
+        <x:v>取消/重建/终态锁定与实际完成竞争通过，只有一个终态；双真机业务操作尚待验收。 详见开发记录/2026-10-04-实际餐单确认.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="78" customHeight="1">
       <x:c r="A53" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B53" s="6" t="str">
         <x:v>DEV-046</x:v>
@@ -3175,14 +3269,18 @@
         <x:v>FR-BILL-05、FR-BILL-07、FR-MSG-12
 技术§9.1</x:v>
       </x:c>
-      <x:c r="K53" s="11"/>
+      <x:c r="K53" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L53" s="12"/>
       <x:c r="M53" s="12"/>
-      <x:c r="N53" s="11"/>
+      <x:c r="N53" s="11" t="str">
+        <x:v>到点只生成一次事件，实际确认入口已接入，完成撤销旧提醒通过；官方微信提醒发送待接入。 详见开发记录/2026-10-04-实际餐单确认.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="78" customHeight="1">
       <x:c r="A54" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B54" s="6" t="str">
         <x:v>DEV-047</x:v>
@@ -3212,14 +3310,18 @@
         <x:v>FR-MSG-01、FR-MSG-02、FR-MSG-03、FR-MSG-04、FR-MSG-11
 技术§3.7、9</x:v>
       </x:c>
-      <x:c r="K54" s="11"/>
+      <x:c r="K54" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L54" s="12"/>
       <x:c r="M54" s="12"/>
-      <x:c r="N54" s="11"/>
+      <x:c r="N54" s="11" t="str">
+        <x:v>首次下单发送已实现，预约时间字段待确认；追加、修改、取消暂无匹配获批模板，保留站内事件。 详见开发记录/2026-10-05-微信订阅通知.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="55" ht="78" customHeight="1">
       <x:c r="A55" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B55" s="6" t="str">
         <x:v>DEV-048</x:v>
@@ -3249,14 +3351,18 @@
         <x:v>FR-MSG-08
 技术§9.3</x:v>
       </x:c>
-      <x:c r="K55" s="11"/>
+      <x:c r="K55" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L55" s="12"/>
       <x:c r="M55" s="12"/>
-      <x:c r="N55" s="11"/>
+      <x:c r="N55" s="11" t="str">
+        <x:v>主动点击授权、拒绝不阻断、同键记账及超时补登记通过；评价入口已接，主厨入口待时间字段确认和真机授权。 详见开发记录/2026-10-05-微信订阅通知.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="56" ht="78" customHeight="1">
       <x:c r="A56" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B56" s="6" t="str">
         <x:v>DEV-049</x:v>
@@ -3280,20 +3386,24 @@
         <x:v>Outbox表、订阅授权</x:v>
       </x:c>
       <x:c r="I56" s="6" t="str">
-        <x:v>行锁领取、网络5xx退避、明确拒绝不重试；检查最新状态；失败不回滚订单；站内可查，不假称送达。</x:v>
+        <x:v>行锁领取，明确未成功的繁忙/限流/token错误最多3次；超时/非200结果不明不自动重发；检查最新状态，失败不回滚业务，不假称送达。</x:v>
       </x:c>
       <x:c r="J56" s="6" t="str">
         <x:v>FR-MSG-10
 技术§3.7、9.2</x:v>
       </x:c>
-      <x:c r="K56" s="11"/>
+      <x:c r="K56" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L56" s="12"/>
       <x:c r="M56" s="12"/>
-      <x:c r="N56" s="11"/>
+      <x:c r="N56" s="11" t="str">
+        <x:v>行锁预占、并发去重、明确失败最多3次、超时不重发及5分钟崩溃恢复通过；业务不回滚，微信回执待验收。 详见开发记录/2026-10-05-微信订阅通知.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="57" ht="78" customHeight="1">
       <x:c r="A57" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B57" s="6" t="str">
         <x:v>DEV-050</x:v>
@@ -3323,14 +3433,18 @@
         <x:v>FR-DATA-05
 技术§8.4、10.5、12.1</x:v>
       </x:c>
-      <x:c r="K57" s="11"/>
+      <x:c r="K57" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L57" s="12"/>
       <x:c r="M57" s="12"/>
-      <x:c r="N57" s="11"/>
+      <x:c r="N57" s="11" t="str">
+        <x:v>活动编辑前后快照、成员移除及邀请轮换与事务一致，原垫付不丢失；其他领域完整差异后续。 详见开发记录/2026-10-05-聚会信息与成员管理.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="58" ht="78" customHeight="1">
       <x:c r="A58" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B58" s="6" t="str">
         <x:v>DEV-051</x:v>
@@ -3360,14 +3474,18 @@
         <x:v>FR-HOME-01、FR-HOME-02、FR-HOME-06
 技术§3.5、5.5</x:v>
       </x:c>
-      <x:c r="K58" s="11"/>
+      <x:c r="K58" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L58" s="12"/>
       <x:c r="M58" s="12"/>
-      <x:c r="N58" s="11"/>
+      <x:c r="N58" s="11" t="str">
+        <x:v>北京时间问候、默认全家本周、周/月/年与现有单店筛选、真实零值及请求竞争通过；模板编译、页面状态测试和模拟器真实零值/周期/未来月份/点餐入口通过，单店滚轮与非空双真机待验收。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="59" ht="78" customHeight="1">
       <x:c r="A59" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B59" s="6" t="str">
         <x:v>DEV-052</x:v>
@@ -3397,14 +3515,18 @@
         <x:v>FR-HOME-03、FR-HOME-04、FR-HOME-05、FR-ORD-11
 技术§3.5、6.5</x:v>
       </x:c>
-      <x:c r="K59" s="11"/>
+      <x:c r="K59" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L59" s="12"/>
       <x:c r="M59" s="12"/>
-      <x:c r="N59" s="11"/>
+      <x:c r="N59" s="11" t="str">
+        <x:v>按用餐日期与最终实际菜统计，跨规格一次、跨店分开、晚确认回补、零与未来趋势、并列稳定排行、有效HOT前5、缓存换代通过；双真机待验收。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="78" customHeight="1">
       <x:c r="A60" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B60" s="6" t="str">
         <x:v>DEV-053</x:v>
@@ -3434,14 +3556,18 @@
         <x:v>FR-HOME-07、FR-HOME-08、FR-HOME-09、FR-HOME-10
 技术§3.5</x:v>
       </x:c>
-      <x:c r="K60" s="11"/>
+      <x:c r="K60" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L60" s="12"/>
       <x:c r="M60" s="12"/>
-      <x:c r="N60" s="11"/>
+      <x:c r="N60" s="11" t="str">
+        <x:v>当日推荐MySQL持久化、Redis清空不换菜、失效立即替换/隐藏、并发一致、跨店不自动加菜、终态/过季及未核对请求保留通过；真实非空设备待验收。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="61" ht="78" customHeight="1">
       <x:c r="A61" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B61" s="6" t="str">
         <x:v>DEV-054</x:v>
@@ -3471,14 +3597,18 @@
         <x:v>FR-ME-05
 技术§3.5、5.5</x:v>
       </x:c>
-      <x:c r="K61" s="11"/>
+      <x:c r="K61" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L61" s="12"/>
       <x:c r="M61" s="12"/>
-      <x:c r="N61" s="11"/>
+      <x:c r="N61" s="11" t="str">
+        <x:v>本人评价与原点单邀约分页、回看和修改入口已接入；模拟器空态核对，双真机待验收。 详见开发记录/2026-10-04-评价分享.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="62" ht="78" customHeight="1">
       <x:c r="A62" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B62" s="6" t="str">
         <x:v>DEV-055</x:v>
@@ -3508,14 +3638,18 @@
         <x:v>FR-BILL-06、FR-BILL-20
 技术§3.4、8.4</x:v>
       </x:c>
-      <x:c r="K62" s="11"/>
+      <x:c r="K62" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L62" s="12"/>
       <x:c r="M62" s="12"/>
-      <x:c r="N62" s="11"/>
+      <x:c r="N62" s="11" t="str">
+        <x:v>本店主厨、用餐日已到、跨日补确认、下架过季补选、原快照保留、至少一道、同事务完成通过；非空设备待验收。 详见开发记录/2026-10-04-实际餐单确认.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="63" ht="78" customHeight="1">
       <x:c r="A63" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B63" s="6" t="str">
         <x:v>DEV-056</x:v>
@@ -3545,14 +3679,18 @@
         <x:v>FR-BILL-03、FR-DATA-01
 技术§3.4、6.4</x:v>
       </x:c>
-      <x:c r="K63" s="11"/>
+      <x:c r="K63" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L63" s="12"/>
       <x:c r="M63" s="12"/>
-      <x:c r="N63" s="11"/>
+      <x:c r="N63" s="11" t="str">
+        <x:v>实际与原点单分表，补菜标注、规格合并、未提交不计入与完成冻结通过；历史图片及双真机后续验收。 详见开发记录/2026-10-04-实际餐单确认.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="64" ht="78" customHeight="1">
       <x:c r="A64" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B64" s="6" t="str">
         <x:v>DEV-057</x:v>
@@ -3582,14 +3720,18 @@
         <x:v>FR-BILL-08、FR-MSG-06
 技术§3.5、3.7</x:v>
       </x:c>
-      <x:c r="K64" s="11"/>
+      <x:c r="K64" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L64" s="12"/>
       <x:c r="M64" s="12"/>
-      <x:c r="N64" s="11"/>
+      <x:c r="N64" s="11" t="str">
+        <x:v>所有原点单者去重事件已接6633字段和发送worker，完整7天期限校验通过；授权与真实微信跳转待验收。 详见开发记录/2026-10-05-微信订阅通知.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="78" customHeight="1">
       <x:c r="A65" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B65" s="6" t="str">
         <x:v>DEV-058</x:v>
@@ -3619,14 +3761,18 @@
         <x:v>FR-BILL-14、FR-BILL-15、FR-BILL-16、FR-BILL-17、FR-BILL-18
 技术§3.5、5.5</x:v>
       </x:c>
-      <x:c r="K65" s="11"/>
+      <x:c r="K65" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L65" s="12"/>
       <x:c r="M65" s="12"/>
-      <x:c r="N65" s="11"/>
+      <x:c r="N65" s="11" t="str">
+        <x:v>实际菜唯一评分及实时均分/条数已接入，菜单/HOT展示和首页评分缓存换代通过；双真机待验收。 详见开发记录/2026-10-04-首页统计.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="78" customHeight="1">
       <x:c r="A66" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B66" s="6" t="str">
         <x:v>DEV-059</x:v>
@@ -3656,14 +3802,18 @@
         <x:v>FR-BILL-19
 技术§3.5</x:v>
       </x:c>
-      <x:c r="K66" s="11"/>
+      <x:c r="K66" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L66" s="12"/>
       <x:c r="M66" s="12"/>
-      <x:c r="N66" s="11"/>
+      <x:c r="N66" s="11" t="str">
+        <x:v>完成后7天和首次提交后24小时截止、一次修改、本人权限、超时同键重试与并发修改通过；双真机待验收。 详见开发记录/2026-10-04-评价分享.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="78" customHeight="1">
       <x:c r="A67" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B67" s="6" t="str">
         <x:v>DEV-060</x:v>
@@ -3693,14 +3843,18 @@
         <x:v>FR-AUTH-11、FR-BILL-21、FR-MSG-13
 技术§3.5、5.5、10.2</x:v>
       </x:c>
-      <x:c r="K67" s="11"/>
+      <x:c r="K67" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L67" s="12"/>
       <x:c r="M67" s="12"/>
-      <x:c r="N67" s="11"/>
+      <x:c r="N67" s="11" t="str">
+        <x:v>7天分享、授权登录、受限凭证、过期只读及不延长截止通过，令牌仅存哈希；真实微信转发与双真机待验收。 详见开发记录/2026-10-04-评价分享.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" ht="78" customHeight="1">
       <x:c r="A68" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B68" s="6" t="str">
         <x:v>DEV-061</x:v>
@@ -3730,14 +3884,18 @@
         <x:v>FR-ME-06
 技术§3.1、5.6</x:v>
       </x:c>
-      <x:c r="K68" s="11"/>
+      <x:c r="K68" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L68" s="12"/>
       <x:c r="M68" s="12"/>
-      <x:c r="N68" s="11"/>
+      <x:c r="N68" s="11" t="str">
+        <x:v>个人中心“我参加的聚会”接入8083本人列表；当前/历史及曾参与只读，密令过期保留原聚会资格，双真机待验收。 详见开发记录/2026-10-05-聚会基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="69" ht="78" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B69" s="6" t="str">
         <x:v>DEV-062</x:v>
@@ -3767,14 +3925,18 @@
         <x:v>FR-PARTY-01、FR-PARTY-02、FR-PARTY-04
 技术§3.6、5.6</x:v>
       </x:c>
-      <x:c r="K69" s="11"/>
+      <x:c r="K69" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L69" s="12"/>
       <x:c r="M69" s="12"/>
-      <x:c r="N69" s="11"/>
+      <x:c r="N69" s="11" t="str">
+        <x:v>创建、修改时间及四款预设封面已接通；同键恢复、冲突保稿及权限回归通过，双真机待验收。 详见开发记录/2026-10-08-聚会预设封面.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="70" ht="78" customHeight="1">
       <x:c r="A70" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B70" s="6" t="str">
         <x:v>DEV-063</x:v>
@@ -3804,14 +3966,18 @@
         <x:v>FR-AUTH-05、FR-AUTH-10、FR-PARTY-03、FR-PARTY-19、FR-MSG-07
 技术§3.6、5.6、10.2</x:v>
       </x:c>
-      <x:c r="K70" s="11"/>
+      <x:c r="K70" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L70" s="12"/>
       <x:c r="M70" s="12"/>
-      <x:c r="N70" s="11"/>
+      <x:c r="N70" s="11" t="str">
+        <x:v>保存封面用于分享，默认回退及未报名隐私通过测试；邀请轮换已接通，真实微信分享待验收。 详见开发记录/2026-10-08-聚会预设封面.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="71" ht="78" customHeight="1">
       <x:c r="A71" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B71" s="6" t="str">
         <x:v>DEV-064</x:v>
@@ -3841,14 +4007,18 @@
         <x:v>FR-PARTY-05、FR-PARTY-06、FR-PARTY-07、FR-PARTY-18
 技术§3.6</x:v>
       </x:c>
-      <x:c r="K71" s="11"/>
+      <x:c r="K71" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L71" s="12"/>
       <x:c r="M71" s="12"/>
-      <x:c r="N71" s="11"/>
+      <x:c r="N71" s="11" t="str">
+        <x:v>一账号一人、幂等及并发去重、100人上限、退出前拦截待采购、已购垫付保留、再次报名与创建者不可退出通过；双真机待验收。 详见开发记录/2026-10-05-聚会基础.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="72" ht="78" customHeight="1">
       <x:c r="A72" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B72" s="6" t="str">
         <x:v>DEV-065</x:v>
@@ -3878,14 +4048,18 @@
         <x:v>FR-PARTY-20
 技术§3.6、10</x:v>
       </x:c>
-      <x:c r="K72" s="11"/>
+      <x:c r="K72" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L72" s="12"/>
       <x:c r="M72" s="12"/>
-      <x:c r="N72" s="11"/>
+      <x:c r="N72" s="11" t="str">
+        <x:v>创建者软移除、待采购先解除、垫付历史保留及旧邀请失效通过；二次确认、账号隔离、跨页同键核对已接；真机待验收。 详见开发记录/2026-10-05-聚会信息与成员管理.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" ht="78" customHeight="1">
       <x:c r="A73" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B73" s="6" t="str">
         <x:v>DEV-066</x:v>
@@ -3915,14 +4089,18 @@
         <x:v>FR-PARTY-08、FR-PARTY-09
 技术§3.6、5.6</x:v>
       </x:c>
-      <x:c r="K73" s="11"/>
+      <x:c r="K73" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L73" s="12"/>
       <x:c r="M73" s="12"/>
-      <x:c r="N73" s="11"/>
+      <x:c r="N73" s="11" t="str">
+        <x:v>成员新增、20/10可见字、500项容量和每页20项通过；两行采购页面已接通，非空窄屏待验收。 详见开发记录/2026-10-05-聚会采购.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="74" ht="78" customHeight="1">
       <x:c r="A74" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B74" s="6" t="str">
         <x:v>DEV-067</x:v>
@@ -3952,14 +4130,18 @@
         <x:v>FR-PARTY-10、FR-PARTY-11
 技术§3.6、8.2</x:v>
       </x:c>
-      <x:c r="K74" s="11"/>
+      <x:c r="K74" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L74" s="12"/>
       <x:c r="M74" s="12"/>
-      <x:c r="N74" s="11"/>
+      <x:c r="N74" s="11" t="str">
+        <x:v>创建者指定、成员自认领及解除、版本与条件更新通过；并发仅一人成功，失败后可看当前负责人。 详见开发记录/2026-10-05-聚会采购.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" ht="78" customHeight="1">
       <x:c r="A75" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B75" s="6" t="str">
         <x:v>DEV-068</x:v>
@@ -3989,14 +4171,18 @@
         <x:v>FR-PARTY-12、FR-PARTY-13、FR-PARTY-22
 技术§3.6、6.4</x:v>
       </x:c>
-      <x:c r="K75" s="11"/>
+      <x:c r="K75" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L75" s="12"/>
       <x:c r="M75" s="12"/>
-      <x:c r="N75" s="11"/>
+      <x:c r="N75" s="11" t="str">
+        <x:v>负责人/创建者购买、精确金额、0元说明、单一垫付人通过；小程序购买表单和确认已接通。 详见开发记录/2026-10-05-聚会采购.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" ht="78" customHeight="1">
       <x:c r="A76" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B76" s="6" t="str">
         <x:v>DEV-069</x:v>
@@ -4026,14 +4212,18 @@
         <x:v>FR-PARTY-15、FR-PARTY-21
 技术§3.6、8.4</x:v>
       </x:c>
-      <x:c r="K76" s="11"/>
+      <x:c r="K76" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L76" s="12"/>
       <x:c r="M76" s="12"/>
-      <x:c r="N76" s="11"/>
+      <x:c r="N76" s="11" t="str">
+        <x:v>编辑权限、已购移除原因确认、创建者更正付款人、撤回及前后审计通过；真机纠错流程待验收。 详见开发记录/2026-10-05-聚会采购.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" ht="78" customHeight="1">
       <x:c r="A77" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B77" s="6" t="str">
         <x:v>DEV-070</x:v>
@@ -4063,14 +4253,18 @@
         <x:v>FR-PARTY-14
 技术§3.6、5.6</x:v>
       </x:c>
-      <x:c r="K77" s="11"/>
+      <x:c r="K77" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L77" s="12"/>
       <x:c r="M77" s="12"/>
-      <x:c r="N77" s="11"/>
+      <x:c r="N77" s="11" t="str">
+        <x:v>已移除成员保留真实垫付与只读账单，人均按剩余报名人数更新；90元2人变1人的45到90参考额回归通过。 详见开发记录/2026-10-05-聚会信息与成员管理.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="78" customHeight="1">
       <x:c r="A78" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B78" s="6" t="str">
         <x:v>DEV-071</x:v>
@@ -4100,14 +4294,18 @@
         <x:v>FR-PARTY-16、FR-PARTY-23、FR-DATA-03
 技术§3.6、4.4、8.4</x:v>
       </x:c>
-      <x:c r="K78" s="11"/>
+      <x:c r="K78" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L78" s="12"/>
       <x:c r="M78" s="12"/>
-      <x:c r="N78" s="11"/>
+      <x:c r="N78" s="11" t="str">
+        <x:v>手动结束后采购/报名只读、重开补录按原权限、首次结束保留通过；多人真机全流程待验收。 详见开发记录/2026-10-05-聚会采购.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" ht="78" customHeight="1">
       <x:c r="A79" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>△ 待验收</x:v>
       </x:c>
       <x:c r="B79" s="6" t="str">
         <x:v>DEV-072</x:v>
@@ -4137,10 +4335,14 @@
         <x:v>FR-PARTY-17
 技术§5.6</x:v>
       </x:c>
-      <x:c r="K79" s="11"/>
+      <x:c r="K79" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L79" s="12"/>
       <x:c r="M79" s="12"/>
-      <x:c r="N79" s="11"/>
+      <x:c r="N79" s="11" t="str">
+        <x:v>本人当前/历史列表及详情展示已选封面，保留历史引用；账单可回看，非空真机待验收。 详见开发记录/2026-10-08-聚会预设封面.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" ht="78" customHeight="1">
       <x:c r="A80" s="11" t="str">
@@ -4329,7 +4531,7 @@
     </x:row>
     <x:row r="85" ht="78" customHeight="1">
       <x:c r="A85" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B85" s="6" t="str">
         <x:v>DEV-078</x:v>
@@ -4359,10 +4561,14 @@
         <x:v>FR-MSG-09
 技术§3.7、9.2</x:v>
       </x:c>
-      <x:c r="K85" s="11"/>
+      <x:c r="K85" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L85" s="12"/>
       <x:c r="M85" s="12"/>
-      <x:c r="N85" s="11"/>
+      <x:c r="N85" s="11" t="str">
+        <x:v>固定30秒合并、终态撤销及发送前最新状态/7天校验通过；变更与到点通知尚无获批模板，不挪用新订单模板。 详见开发记录/2026-10-05-微信订阅通知.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" ht="78" customHeight="1">
       <x:c r="A86" s="11" t="str">
@@ -4477,7 +4683,7 @@
     </x:row>
     <x:row r="89" ht="78" customHeight="1">
       <x:c r="A89" s="11" t="str">
-        <x:v>☐ 未开始</x:v>
+        <x:v>◐ 进行中</x:v>
       </x:c>
       <x:c r="B89" s="6" t="str">
         <x:v>DEV-082</x:v>
@@ -4507,10 +4713,14 @@
         <x:v>FR-UI-13
 技术§10.3、11</x:v>
       </x:c>
-      <x:c r="K89" s="11"/>
+      <x:c r="K89" s="11" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
       <x:c r="L89" s="12"/>
       <x:c r="M89" s="12"/>
-      <x:c r="N89" s="11"/>
+      <x:c r="N89" s="11" t="str">
+        <x:v>移除成员提示垫付保留、人数变化及旧邀请失效，二次确认后提交；既有采购与结束确认通过，全局真机后续。 详见开发记录/2026-10-05-聚会信息与成员管理.md。</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="78" customHeight="1">
       <x:c r="A90" s="11" t="str">
@@ -4750,7 +4960,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48f0b45653a2478f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R182238eba5304ed6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5626,7 +5836,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4a39b9adcb04aa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a6f742335f94b15"/>
   </x:tableParts>
 </x:worksheet>
 </file>